--- a/imageCreationExcel/Bright/Master/MASTER_5.xlsx
+++ b/imageCreationExcel/Bright/Master/MASTER_5.xlsx
@@ -552,15 +552,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\2_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>M_5_1_D_filler_2_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_5_1_D_filler_2_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -606,15 +612,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\3_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>M_5_2_J_filler_3_day_sun_empty_MODEL.jpg</t>
+          <t>M_5_2_J_filler_3_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -660,15 +684,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\4_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>M_5_3_6_unmatch_4_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_5_3_6_unmatch_4_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -768,15 +798,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\1_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>M_5_5_1_match_1_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_5_5_1_match_1_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -876,15 +912,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\0_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>M_5_7_0_match_0_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_5_7_0_match_0_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -930,15 +972,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>M_5_8_J_filler_7_day_sun_empty_MODEL.jpg</t>
+          <t>M_5_8_J_filler_7_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -984,15 +1044,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\9_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>M_5_9_8_unmatch_9_day_sun_busy_MODEL.jpg</t>
+          <t>M_5_9_8_unmatch_9_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1038,15 +1116,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\4_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>M_5_10_L_filler_4_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_5_10_L_filler_4_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1146,15 +1230,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\0_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>M_5_12_4_unmatch_0_day_rain_busy_MODEL.jpg</t>
+          <t>M_5_12_4_unmatch_0_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1200,15 +1302,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\6_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>M_5_13_S_filler_6_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_5_13_S_filler_6_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -1362,15 +1470,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\1_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>M_5_16_1_match_1_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_5_16_1_match_1_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1416,15 +1530,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\3_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>M_5_17_E_filler_3_day_rain_empty_MODEL.jpg</t>
+          <t>M_5_17_E_filler_3_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1470,15 +1602,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\1_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>M_5_18_0_unmatch_1_day_rain_busy_MODEL.jpg</t>
+          <t>M_5_18_0_unmatch_1_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1524,15 +1674,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\1_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>M_5_19_J_filler_1_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_5_19_J_filler_1_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1578,15 +1734,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\3_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>M_5_20_I_filler_3_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_5_20_I_filler_3_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1686,15 +1848,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\5_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>M_5_22_F_filler_5_day_rain_empty_MODEL.jpg</t>
+          <t>M_5_22_F_filler_5_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1740,15 +1920,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\6_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>M_5_23_R_filler_6_day_rain_busy_MODEL.jpg</t>
+          <t>M_5_23_R_filler_6_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1902,15 +2100,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\3_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>M_5_26_3_match_3_day_sun_empty_MODEL.jpg</t>
+          <t>M_5_26_3_match_3_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2010,15 +2226,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\7_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>M_5_28_B_filler_7_day_rain_empty_MODEL.jpg</t>
+          <t>M_5_28_B_filler_7_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2064,15 +2298,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\2_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>M_5_29_E_filler_2_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_5_29_E_filler_2_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2358,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\8_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>M_5_30_7_unmatch_8_day_sun_empty_MODEL.jpg</t>
+          <t>M_5_30_7_unmatch_8_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2226,15 +2484,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\5_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>M_5_32_C_filler_5_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_5_32_C_filler_5_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2388,15 +2652,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\8_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>M_5_35_I_filler_8_day_rain_busy_MODEL.jpg</t>
+          <t>M_5_35_I_filler_8_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2442,15 +2724,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>M_5_36_Q_filler_7_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_5_36_Q_filler_7_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2496,15 +2784,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\2_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>M_5_37_A_filler_2_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_5_37_A_filler_2_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2844,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\3_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>M_5_38_B_filler_3_day_sun_busy_MODEL.jpg</t>
+          <t>M_5_38_B_filler_3_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2604,15 +2916,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\9_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>M_5_39_9_match_9_day_rain_empty_MODEL.jpg</t>
+          <t>M_5_39_9_match_9_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2712,15 +3042,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\6_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>M_5_41_J_filler_6_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_5_41_J_filler_6_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2820,15 +3156,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\6_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>M_5_43_7_unmatch_6_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_5_43_7_unmatch_6_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -2874,15 +3216,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\1_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>M_5_44_B_filler_1_day_sun_busy_MODEL.jpg</t>
+          <t>M_5_44_B_filler_1_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2982,15 +3342,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\0_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>M_5_46_P_filler_0_day_rain_empty_MODEL.jpg</t>
+          <t>M_5_46_P_filler_0_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -3090,15 +3468,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\0_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>M_5_48_P_filler_0_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_5_48_P_filler_0_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
